--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>227</v>
+        <v>322</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03851</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L12" s="12" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>03851</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -983,47 +983,47 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L15" s="12" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03543</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,47 +1091,47 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03543</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>0</v>
@@ -1274,14 +1274,14 @@
         <v>2</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1526,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>156</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1474358974358974</v>
+        <v>23</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>66</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.4696969696969697</v>
+        <v>31</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>47</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.5957446808510638</v>
+        <v>28</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.09259259259259259</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>2</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.06</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>31</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.3225806451612903</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>39</v>
@@ -833,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>21</v>
@@ -842,14 +842,14 @@
         <v>19</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -983,47 +983,47 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1094,13 +1094,13 @@
         <v>30</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>20</v>
@@ -1112,14 +1112,14 @@
         <v>11</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
@@ -1166,14 +1166,14 @@
         <v>1</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -1134,11 +1134,7 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>TBD</t>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>24</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>30</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>22</v>
@@ -995,16 +995,16 @@
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>5</v>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>9</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
         <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>9</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,19 +821,19 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>22</v>
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>14</v>
@@ -995,35 +995,35 @@
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03543</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="G15" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03543</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1141,22 +1141,22 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>1</v>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>3</v>
@@ -1216,7 +1216,7 @@
         <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>39</v>
@@ -833,19 +833,19 @@
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>25</v>
@@ -995,35 +995,35 @@
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03543</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03543</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1141,28 +1141,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13</v>
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -1134,7 +1134,11 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>TBD</t>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1296,11 +1296,7 @@
           <t>ALA</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1350,11 +1346,7 @@
           <t>TRENTO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1404,11 +1396,7 @@
           <t>SONA</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1512,11 +1500,7 @@
           <t>VERONA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -1566,11 +1550,7 @@
           <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>TBD</t>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N25" headerRowCount="1">
-  <autoFilter ref="A10:N25"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O25" headerRowCount="1">
+  <autoFilter ref="A10:O25"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIALE DEL LAVORO 22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA G.MAMELI 160/F</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA VENEZIA 76</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA GARDESANA 25</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIALE CARDUCCI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA GAROFOLI N. 270</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA POSTUMIA N.  86</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA CAMPAGNOL DI TOMBETTA 6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1296,27 +1357,29 @@
           <t>ALA</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>S.S. 12 KM 337+947 SNC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" s="12" t="n">
         <v>0</v>
       </c>
@@ -1329,7 +1392,10 @@
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1346,27 +1412,29 @@
           <t>TRENTO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>VIALE VERONA</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" s="12" t="n">
         <v>0</v>
       </c>
@@ -1379,7 +1447,10 @@
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1396,21 +1467,23 @@
           <t>SONA</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>LOCALITA' CIVEL 1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
@@ -1429,7 +1502,10 @@
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1448,29 +1524,31 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA VILLAFRANCA 357</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" s="12" t="n">
         <v>0</v>
       </c>
@@ -1478,12 +1556,15 @@
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1500,27 +1581,29 @@
           <t>VERONA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VIA MANTOVANA 90</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="12" t="n">
         <v>0</v>
       </c>
@@ -1533,7 +1616,10 @@
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1550,21 +1636,23 @@
           <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>VIA SAN GIOVANI PAGLIA 23</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
@@ -1583,7 +1671,10 @@
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>42</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>51</v>
-      </c>
       <c r="H13" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>23</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>3</v>
@@ -1037,13 +1037,13 @@
         <v>14</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>13</v>
@@ -1158,10 +1158,10 @@
         <v>16</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
@@ -1217,14 +1217,14 @@
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1276,14 +1276,14 @@
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G13" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="H13" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="K13" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>6</v>
@@ -1099,7 +1099,7 @@
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>6</v>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>25</v>
@@ -1155,17 +1155,17 @@
         <v>7</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>6</v>
@@ -1276,14 +1276,14 @@
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>22</v>
@@ -863,14 +863,14 @@
         <v>22</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>6</v>
@@ -1140,13 +1140,13 @@
         <v>41</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>25</v>
@@ -1158,14 +1158,14 @@
         <v>17</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
@@ -1267,16 +1267,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>22</v>
@@ -863,14 +863,14 @@
         <v>22</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
@@ -922,14 +922,14 @@
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>38</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>29</v>
@@ -1031,7 +1031,7 @@
         <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>15</v>
@@ -1040,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>3</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03543</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE CARDUCCI</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,52 +1137,52 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="M16" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03543</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIALE CARDUCCI</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1276,14 +1276,14 @@
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H13" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="J13" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>3</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>0</v>
@@ -1155,17 +1155,17 @@
         <v>19</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>13</v>
@@ -1208,7 +1208,7 @@
         <v>16</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>7</v>
@@ -1217,7 +1217,7 @@
         <v>17</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>5</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
@@ -1273,17 +1273,17 @@
         <v>7</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>27</v>
@@ -972,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>30</v>
@@ -981,14 +981,14 @@
         <v>11</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA GARDESANA 25</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,52 +1078,52 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIA GARDESANA 25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
@@ -1270,20 +1270,20 @@
         <v>17</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>3</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>545</v>
+        <v>578</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA 76</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,52 +1019,52 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIA VENEZIA 76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>77</v>
@@ -1149,19 +1149,19 @@
         <v>20</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>7</v>
@@ -1217,14 +1217,14 @@
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>9</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>3</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O25" headerRowCount="1">
-  <autoFilter ref="A10:O25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O12" headerRowCount="1">
+  <autoFilter ref="A10:O12"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,13 +521,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>578</v>
+        <v>63</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>468</v>
+        <v>62</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,22 +818,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03838</t>
+          <t>01280</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEL LAVORO 22</t>
+          <t>VIALE ITALIA 160</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>335</v>
+        <v>93</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,22 +877,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>01288</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>BOLANO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VIA CISA 50</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -901,782 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>03851</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>VERONA</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>VIA G.MAMELI 160/F</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>03775</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>VIA GAROFOLI N. 270</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>03817</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>PESCHIERA DEL GARDA</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>VIA VENEZIA 76</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>03793</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>BUSSOLENGO</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>VIA GARDESANA 25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>03543</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>RIVA DEL GARDA</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>VIALE CARDUCCI</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>51516</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>VILLAFRANCA DI VERONA</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>VIA POSTUMIA N.  86</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>03826</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>VERONA</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>VIA CAMPAGNOL DI TOMBETTA 6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>03465</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ALA</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>S.S. 12 KM 337+947 SNC</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>03538</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>TRENTO</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>VIALE VERONA</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>03816</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SONA</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>LOCALITA' CIVEL 1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>13862</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>VALEGGIO SUL MINCIO</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>VIA VILLAFRANCA 357</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
           <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>57208</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>VERONA</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>VIA MANTOVANA 90</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>55905</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>VILLAFRANCA DI VERONA</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>VIA SAN GIOVANI PAGLIA 23</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - TBD.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,13 +684,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>23</v>
@@ -854,7 +854,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>7</v>
@@ -863,14 +863,14 @@
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>25</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>4</v>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>0</v>
